--- a/src/locales/lang.xlsx
+++ b/src/locales/lang.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="20752" windowHeight="8955"/>
+    <workbookView windowWidth="25600" windowHeight="12120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26188,13 +26188,13 @@
     <t>h5.home.desc_p1</t>
   </si>
   <si>
-    <t>超一百萬用戶加入</t>
+    <t>世界美股通用交易平臺，超一百萬用戶加入</t>
   </si>
   <si>
     <t>Mehr als eine Million Nutzer beigetreten</t>
   </si>
   <si>
-    <t>Over 1 million users joined</t>
+    <t>Worldwide Universal US Stock Trading Platform — over 1 million users have joined</t>
   </si>
   <si>
     <t>Plus d'un million d'utilisateurs ont rejoint</t>
@@ -26236,7 +26236,7 @@
     <t>Ponad milion użytkowników dołączyło</t>
   </si>
   <si>
-    <t>超一百万用户加入</t>
+    <t>全球通用美股交易平台 — 超过一百万用户已加入</t>
   </si>
   <si>
     <t>h5.home.desc_p2</t>
@@ -42180,7 +42180,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -42226,6 +42226,12 @@
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -42380,9 +42386,22 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF0D0D0D"/>
+      <name val="Tahoma"/>
+      <charset val="222"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -42393,9 +42412,14 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0D0D0D"/>
       <name val="Tahoma"/>
       <charset val="222"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -42410,9 +42434,11 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
-      <name val="Tahoma"/>
-      <charset val="222"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -42422,33 +42448,13 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
@@ -42805,31 +42811,28 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -42838,120 +42841,123 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -42991,60 +42997,61 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
     <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -43257,25 +43264,25 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R829"/>
-  <sheetFormatPr defaultColWidth="12.6371681415929" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.6363636363636" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="30.5398230088496" style="5" customWidth="1"/>
-    <col min="2" max="2" width="24.3716814159292" style="5" customWidth="1"/>
-    <col min="3" max="3" width="31.5575221238938" style="5" customWidth="1"/>
-    <col min="4" max="4" width="33.4867256637168" style="5" customWidth="1"/>
-    <col min="5" max="5" width="19.3362831858407" style="5" customWidth="1"/>
-    <col min="6" max="6" width="17.0973451327434" style="5" customWidth="1"/>
-    <col min="7" max="7" width="18.3451327433628" style="5" customWidth="1"/>
-    <col min="8" max="8" width="24.6814159292035" style="5" customWidth="1"/>
-    <col min="9" max="9" width="15.7699115044248" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.8230088495575" style="5" customWidth="1"/>
-    <col min="11" max="11" width="24.7345132743363" style="5" customWidth="1"/>
-    <col min="12" max="12" width="17.6017699115044" style="5" customWidth="1"/>
-    <col min="13" max="13" width="18.5929203539823" style="5" customWidth="1"/>
-    <col min="14" max="14" width="17.8141592920354" style="5" customWidth="1"/>
-    <col min="15" max="15" width="23.8672566371681" style="5" customWidth="1"/>
-    <col min="16" max="27" width="17.8141592920354" style="5" customWidth="1"/>
-    <col min="28" max="16384" width="12.6371681415929" style="5"/>
+    <col min="1" max="1" width="30.5363636363636" style="5" customWidth="1"/>
+    <col min="2" max="2" width="24.3727272727273" style="5" customWidth="1"/>
+    <col min="3" max="3" width="31.5545454545455" style="5" customWidth="1"/>
+    <col min="4" max="4" width="33.4909090909091" style="5" customWidth="1"/>
+    <col min="5" max="5" width="19.3363636363636" style="5" customWidth="1"/>
+    <col min="6" max="6" width="17.1" style="5" customWidth="1"/>
+    <col min="7" max="7" width="18.3454545454545" style="5" customWidth="1"/>
+    <col min="8" max="8" width="24.6818181818182" style="5" customWidth="1"/>
+    <col min="9" max="9" width="15.7727272727273" style="5" customWidth="1"/>
+    <col min="10" max="10" width="21.8272727272727" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7363636363636" style="5" customWidth="1"/>
+    <col min="12" max="12" width="17.6" style="5" customWidth="1"/>
+    <col min="13" max="13" width="18.5909090909091" style="5" customWidth="1"/>
+    <col min="14" max="14" width="17.8181818181818" style="5" customWidth="1"/>
+    <col min="15" max="15" width="23.8636363636364" style="5" customWidth="1"/>
+    <col min="16" max="27" width="17.8181818181818" style="5" customWidth="1"/>
+    <col min="28" max="16384" width="12.6363636363636" style="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:18">
@@ -69605,7 +69612,7 @@
       <c r="C486" s="10" t="s">
         <v>7425</v>
       </c>
-      <c r="D486" s="10" t="s">
+      <c r="D486" s="15" t="s">
         <v>7426</v>
       </c>
       <c r="E486" s="10" t="s">
@@ -69647,7 +69654,7 @@
       <c r="Q486" s="10" t="s">
         <v>7439</v>
       </c>
-      <c r="R486" s="10" t="s">
+      <c r="R486" s="15" t="s">
         <v>7440</v>
       </c>
     </row>
@@ -70271,7 +70278,7 @@
       <c r="A498" s="4" t="s">
         <v>7620</v>
       </c>
-      <c r="B498" s="15" t="s">
+      <c r="B498" s="16" t="s">
         <v>7621</v>
       </c>
       <c r="C498" t="s">

--- a/src/locales/lang.xlsx
+++ b/src/locales/lang.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13878" uniqueCount="12645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14526" uniqueCount="12829">
   <si>
     <t>key</t>
   </si>
@@ -42168,6 +42168,558 @@
   </si>
   <si>
     <t>提现额度太大，请联系管理员</t>
+  </si>
+  <si>
+    <t>B_T_XAU</t>
+  </si>
+  <si>
+    <t>B_T_XAG</t>
+  </si>
+  <si>
+    <t>白銀</t>
+  </si>
+  <si>
+    <t>Silber</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>Argent</t>
+  </si>
+  <si>
+    <t>銀</t>
+  </si>
+  <si>
+    <t>白银</t>
+  </si>
+  <si>
+    <t>B_T_XPT</t>
+  </si>
+  <si>
+    <t>鉑金</t>
+  </si>
+  <si>
+    <t>Platin</t>
+  </si>
+  <si>
+    <t>Platinum</t>
+  </si>
+  <si>
+    <t>Platine</t>
+  </si>
+  <si>
+    <t>白金</t>
+  </si>
+  <si>
+    <t>铂金</t>
+  </si>
+  <si>
+    <t>B_T_XPD</t>
+  </si>
+  <si>
+    <t>鈀金</t>
+  </si>
+  <si>
+    <t>Palladium</t>
+  </si>
+  <si>
+    <t>パラジウム</t>
+  </si>
+  <si>
+    <t>钯金</t>
+  </si>
+  <si>
+    <t>B_hf_HG</t>
+  </si>
+  <si>
+    <t>銅</t>
+  </si>
+  <si>
+    <t>Kupfer</t>
+  </si>
+  <si>
+    <t>Copper</t>
+  </si>
+  <si>
+    <t>Cuivre</t>
+  </si>
+  <si>
+    <t>铜</t>
+  </si>
+  <si>
+    <t>B_fx_sgbpjpy</t>
+  </si>
+  <si>
+    <t>新加坡元/日元</t>
+  </si>
+  <si>
+    <t>Singapur-Dollar / Japanischer Yen</t>
+  </si>
+  <si>
+    <t>Singapore Dollar / Japanese Yen</t>
+  </si>
+  <si>
+    <t>Dollar de Singapour / Yen japonais</t>
+  </si>
+  <si>
+    <t>シンガポール・ドル／日本円</t>
+  </si>
+  <si>
+    <t>B_fx_sgbpusd</t>
+  </si>
+  <si>
+    <t>英鎊/美元</t>
+  </si>
+  <si>
+    <t>Britisches Pfund / US-Dollar</t>
+  </si>
+  <si>
+    <t>British Pound / US Dollar</t>
+  </si>
+  <si>
+    <t>Livre sterling / Dollar américain</t>
+  </si>
+  <si>
+    <t>英ポンド／米ドル</t>
+  </si>
+  <si>
+    <t>英镑/美元</t>
+  </si>
+  <si>
+    <t>B_fx_seurusd</t>
+  </si>
+  <si>
+    <t>歐元/美元</t>
+  </si>
+  <si>
+    <t>Euro / US-Dollar</t>
+  </si>
+  <si>
+    <t>Euro / US Dollar</t>
+  </si>
+  <si>
+    <t>Euro / Dollar américain</t>
+  </si>
+  <si>
+    <t>ユーロ／米ドル</t>
+  </si>
+  <si>
+    <t>欧元/美元</t>
+  </si>
+  <si>
+    <t>B_fx_saudusd</t>
+  </si>
+  <si>
+    <t>澳元/美元</t>
+  </si>
+  <si>
+    <t>Australischer Dollar / US-Dollar</t>
+  </si>
+  <si>
+    <t>Australian Dollar / US Dollar</t>
+  </si>
+  <si>
+    <t>Dollar australien / Dollar américain</t>
+  </si>
+  <si>
+    <t>豪ドル／米ドル</t>
+  </si>
+  <si>
+    <t>B_fx_susdjpy</t>
+  </si>
+  <si>
+    <t>美元/日元</t>
+  </si>
+  <si>
+    <t>US-Dollar / Japanischer Yen</t>
+  </si>
+  <si>
+    <t>US Dollar / Japanese Yen</t>
+  </si>
+  <si>
+    <t>Dollar américain / Yen japonais</t>
+  </si>
+  <si>
+    <t>米ドル／日本円</t>
+  </si>
+  <si>
+    <t>B_fx_seurjpy</t>
+  </si>
+  <si>
+    <t>歐元/日元</t>
+  </si>
+  <si>
+    <t>Euro / Japanischer Yen</t>
+  </si>
+  <si>
+    <t>Euro / Japanese Yen</t>
+  </si>
+  <si>
+    <t>Euro / Yen japonais</t>
+  </si>
+  <si>
+    <t>ユーロ／日本円</t>
+  </si>
+  <si>
+    <t>欧元/日元</t>
+  </si>
+  <si>
+    <t>B_fx_saudjpy</t>
+  </si>
+  <si>
+    <t>澳元/日元</t>
+  </si>
+  <si>
+    <t>Australischer Dollar / Japanischer Yen</t>
+  </si>
+  <si>
+    <t>Australian Dollar / Japanese Yen</t>
+  </si>
+  <si>
+    <t>Dollar australien / Yen japonais</t>
+  </si>
+  <si>
+    <t>豪ドル／日本円</t>
+  </si>
+  <si>
+    <t>B_fx_susdchf</t>
+  </si>
+  <si>
+    <t>美元/瑞郎</t>
+  </si>
+  <si>
+    <t>US-Dollar / Schweizer Franken</t>
+  </si>
+  <si>
+    <t>US Dollar / Swiss Franc</t>
+  </si>
+  <si>
+    <t>Dollar américain / Franc suisse</t>
+  </si>
+  <si>
+    <t>米ドル／スイス・フラン</t>
+  </si>
+  <si>
+    <t>B_fx_schfeur</t>
+  </si>
+  <si>
+    <t>瑞郎/歐元</t>
+  </si>
+  <si>
+    <t>Schweizer Franken / Euro</t>
+  </si>
+  <si>
+    <t>Swiss Franc / Euro</t>
+  </si>
+  <si>
+    <t>Franc suisse / Euro</t>
+  </si>
+  <si>
+    <t>スイス・フラン／ユーロ</t>
+  </si>
+  <si>
+    <t>瑞郎/欧元</t>
+  </si>
+  <si>
+    <t>B_HX_AMD</t>
+  </si>
+  <si>
+    <t>超微半導體</t>
+  </si>
+  <si>
+    <t>Advanced Micro Devices (AMD)</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>超微半导体</t>
+  </si>
+  <si>
+    <t>B_HX_AAPL</t>
+  </si>
+  <si>
+    <t>苹果</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>アップル</t>
+  </si>
+  <si>
+    <t>B_HX_TSLA</t>
+  </si>
+  <si>
+    <t>特斯拉</t>
+  </si>
+  <si>
+    <t>Tesla</t>
+  </si>
+  <si>
+    <t>テスラ</t>
+  </si>
+  <si>
+    <t>B_HX_GOOG</t>
+  </si>
+  <si>
+    <t>谷歌</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>グーグル</t>
+  </si>
+  <si>
+    <t>B_HX_AMZN</t>
+  </si>
+  <si>
+    <t>亞馬遜</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>アマゾン</t>
+  </si>
+  <si>
+    <t>亚马逊</t>
+  </si>
+  <si>
+    <t>B_HX_AIG</t>
+  </si>
+  <si>
+    <t>美國國際集團</t>
+  </si>
+  <si>
+    <t>American International Group (AIG)</t>
+  </si>
+  <si>
+    <t>AIG</t>
+  </si>
+  <si>
+    <t>美国国际集团</t>
+  </si>
+  <si>
+    <t>B_HX_AXP</t>
+  </si>
+  <si>
+    <t>美國運通</t>
+  </si>
+  <si>
+    <t>American Express</t>
+  </si>
+  <si>
+    <t>アメリカン・エキスプレス</t>
+  </si>
+  <si>
+    <t>美国运通</t>
+  </si>
+  <si>
+    <t>B_HX_MSFT</t>
+  </si>
+  <si>
+    <t>微軟</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>マイクロソフト</t>
+  </si>
+  <si>
+    <t>微软</t>
+  </si>
+  <si>
+    <t>B_HX_NVDA</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>英伟达</t>
+  </si>
+  <si>
+    <t>B_HX_META</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>Facebook (Meta)</t>
+  </si>
+  <si>
+    <t>フェイスブック（Meta）</t>
+  </si>
+  <si>
+    <t>B_HX_TSM</t>
+  </si>
+  <si>
+    <t>台積電</t>
+  </si>
+  <si>
+    <t>Taiwan Semiconductor Manufacturing Company (TSMC)</t>
+  </si>
+  <si>
+    <t>TSMC</t>
+  </si>
+  <si>
+    <t>台积电</t>
+  </si>
+  <si>
+    <t>B_HX_GM</t>
+  </si>
+  <si>
+    <t>通用汽車</t>
+  </si>
+  <si>
+    <t>General Motors</t>
+  </si>
+  <si>
+    <t>ゼネラル・モーターズ</t>
+  </si>
+  <si>
+    <t>通用汽车</t>
+  </si>
+  <si>
+    <t>B_HX_DIS</t>
+  </si>
+  <si>
+    <t>迪士尼</t>
+  </si>
+  <si>
+    <t>Disney</t>
+  </si>
+  <si>
+    <t>ディズニー</t>
+  </si>
+  <si>
+    <t>B_HX_COP</t>
+  </si>
+  <si>
+    <t>康菲石油</t>
+  </si>
+  <si>
+    <t>ConocoPhillips</t>
+  </si>
+  <si>
+    <t>コノコフィリップス</t>
+  </si>
+  <si>
+    <t>B_HX_HPQ</t>
+  </si>
+  <si>
+    <t>惠普</t>
+  </si>
+  <si>
+    <t>Hewlett-Packard (HP)</t>
+  </si>
+  <si>
+    <t>HP (Hewlett-Packard)</t>
+  </si>
+  <si>
+    <t>ヒューレット・パッカード（HP）</t>
+  </si>
+  <si>
+    <t>B_HX_SBUX</t>
+  </si>
+  <si>
+    <t>星巴克</t>
+  </si>
+  <si>
+    <t>Starbucks</t>
+  </si>
+  <si>
+    <t>スターバックス</t>
+  </si>
+  <si>
+    <t>B_HX_F</t>
+  </si>
+  <si>
+    <t>福特汽車</t>
+  </si>
+  <si>
+    <t>Ford Motor Company</t>
+  </si>
+  <si>
+    <t>フォード・モーター</t>
+  </si>
+  <si>
+    <t>福特汽车</t>
+  </si>
+  <si>
+    <t>B_HX_NYT</t>
+  </si>
+  <si>
+    <t>紐約時報</t>
+  </si>
+  <si>
+    <t>The New York Times</t>
+  </si>
+  <si>
+    <t>ニューヨーク・タイムズ</t>
+  </si>
+  <si>
+    <t>纽约时报</t>
+  </si>
+  <si>
+    <t>B_HX_ORCL</t>
+  </si>
+  <si>
+    <t>甲骨文</t>
+  </si>
+  <si>
+    <t>Oracle</t>
+  </si>
+  <si>
+    <t>オラクル</t>
+  </si>
+  <si>
+    <t>B_HX_HLT</t>
+  </si>
+  <si>
+    <t>希爾頓酒店</t>
+  </si>
+  <si>
+    <t>Hilton Hotels</t>
+  </si>
+  <si>
+    <t>ヒルトン・ホテルズ</t>
+  </si>
+  <si>
+    <t>希尔顿酒店</t>
+  </si>
+  <si>
+    <t>B_HX_KO</t>
+  </si>
+  <si>
+    <t>可口可樂</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>コカ・コーラ</t>
+  </si>
+  <si>
+    <t>可口可乐</t>
+  </si>
+  <si>
+    <t>B_HX_MCD</t>
+  </si>
+  <si>
+    <t>麥當勞</t>
+  </si>
+  <si>
+    <t>McDonald's</t>
+  </si>
+  <si>
+    <t>マクドナルド</t>
+  </si>
+  <si>
+    <t>麦当劳</t>
   </si>
 </sst>
 </file>
@@ -42386,16 +42938,15 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF0D0D0D"/>
       <name val="Tahoma"/>
       <charset val="222"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -42407,8 +42958,25 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Malgun Gothic"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -42417,9 +42985,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Arial"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -42439,22 +43007,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Malgun Gothic"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
@@ -43263,7 +43815,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:R829"/>
+  <dimension ref="A1:R865"/>
   <sheetFormatPr defaultColWidth="12.6363636363636" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.5363636363636" style="5" customWidth="1"/>
@@ -88226,6 +88778,2022 @@
         <v>12644</v>
       </c>
     </row>
+    <row r="830" customHeight="1" spans="1:18">
+      <c r="A830" s="5" t="s">
+        <v>12645</v>
+      </c>
+      <c r="B830" s="5" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C830" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D830" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E830" s="5" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F830" s="5" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G830" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="H830" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="I830" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="J830" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K830" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="L830" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="M830" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="N830" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="O830" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="P830" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="Q830" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="R830" s="5" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="831" customHeight="1" spans="1:18">
+      <c r="A831" s="5" t="s">
+        <v>12646</v>
+      </c>
+      <c r="B831" s="5" t="s">
+        <v>12647</v>
+      </c>
+      <c r="C831" s="5" t="s">
+        <v>12648</v>
+      </c>
+      <c r="D831" s="5" t="s">
+        <v>12649</v>
+      </c>
+      <c r="E831" s="5" t="s">
+        <v>12650</v>
+      </c>
+      <c r="F831" s="5" t="s">
+        <v>12651</v>
+      </c>
+      <c r="G831" s="5" t="s">
+        <v>12649</v>
+      </c>
+      <c r="H831" s="5" t="s">
+        <v>12649</v>
+      </c>
+      <c r="I831" s="5" t="s">
+        <v>12649</v>
+      </c>
+      <c r="J831" s="5" t="s">
+        <v>12649</v>
+      </c>
+      <c r="K831" s="5" t="s">
+        <v>12649</v>
+      </c>
+      <c r="L831" s="5" t="s">
+        <v>12649</v>
+      </c>
+      <c r="M831" s="5" t="s">
+        <v>12649</v>
+      </c>
+      <c r="N831" s="5" t="s">
+        <v>12649</v>
+      </c>
+      <c r="O831" s="5" t="s">
+        <v>12649</v>
+      </c>
+      <c r="P831" s="5" t="s">
+        <v>12649</v>
+      </c>
+      <c r="Q831" s="5" t="s">
+        <v>12649</v>
+      </c>
+      <c r="R831" s="5" t="s">
+        <v>12652</v>
+      </c>
+    </row>
+    <row r="832" customHeight="1" spans="1:18">
+      <c r="A832" s="5" t="s">
+        <v>12653</v>
+      </c>
+      <c r="B832" s="5" t="s">
+        <v>12654</v>
+      </c>
+      <c r="C832" s="5" t="s">
+        <v>12655</v>
+      </c>
+      <c r="D832" s="5" t="s">
+        <v>12656</v>
+      </c>
+      <c r="E832" s="5" t="s">
+        <v>12657</v>
+      </c>
+      <c r="F832" s="5" t="s">
+        <v>12658</v>
+      </c>
+      <c r="G832" s="5" t="s">
+        <v>12656</v>
+      </c>
+      <c r="H832" s="5" t="s">
+        <v>12656</v>
+      </c>
+      <c r="I832" s="5" t="s">
+        <v>12656</v>
+      </c>
+      <c r="J832" s="5" t="s">
+        <v>12656</v>
+      </c>
+      <c r="K832" s="5" t="s">
+        <v>12656</v>
+      </c>
+      <c r="L832" s="5" t="s">
+        <v>12656</v>
+      </c>
+      <c r="M832" s="5" t="s">
+        <v>12656</v>
+      </c>
+      <c r="N832" s="5" t="s">
+        <v>12656</v>
+      </c>
+      <c r="O832" s="5" t="s">
+        <v>12656</v>
+      </c>
+      <c r="P832" s="5" t="s">
+        <v>12656</v>
+      </c>
+      <c r="Q832" s="5" t="s">
+        <v>12656</v>
+      </c>
+      <c r="R832" s="5" t="s">
+        <v>12659</v>
+      </c>
+    </row>
+    <row r="833" customHeight="1" spans="1:18">
+      <c r="A833" s="5" t="s">
+        <v>12660</v>
+      </c>
+      <c r="B833" s="5" t="s">
+        <v>12661</v>
+      </c>
+      <c r="C833" s="5" t="s">
+        <v>12662</v>
+      </c>
+      <c r="D833" s="5" t="s">
+        <v>12662</v>
+      </c>
+      <c r="E833" s="5" t="s">
+        <v>12662</v>
+      </c>
+      <c r="F833" s="5" t="s">
+        <v>12663</v>
+      </c>
+      <c r="G833" s="5" t="s">
+        <v>12662</v>
+      </c>
+      <c r="H833" s="5" t="s">
+        <v>12662</v>
+      </c>
+      <c r="I833" s="5" t="s">
+        <v>12662</v>
+      </c>
+      <c r="J833" s="5" t="s">
+        <v>12662</v>
+      </c>
+      <c r="K833" s="5" t="s">
+        <v>12662</v>
+      </c>
+      <c r="L833" s="5" t="s">
+        <v>12662</v>
+      </c>
+      <c r="M833" s="5" t="s">
+        <v>12662</v>
+      </c>
+      <c r="N833" s="5" t="s">
+        <v>12662</v>
+      </c>
+      <c r="O833" s="5" t="s">
+        <v>12662</v>
+      </c>
+      <c r="P833" s="5" t="s">
+        <v>12662</v>
+      </c>
+      <c r="Q833" s="5" t="s">
+        <v>12662</v>
+      </c>
+      <c r="R833" s="5" t="s">
+        <v>12664</v>
+      </c>
+    </row>
+    <row r="834" customHeight="1" spans="1:18">
+      <c r="A834" s="5" t="s">
+        <v>12665</v>
+      </c>
+      <c r="B834" s="5" t="s">
+        <v>12666</v>
+      </c>
+      <c r="C834" s="5" t="s">
+        <v>12667</v>
+      </c>
+      <c r="D834" s="5" t="s">
+        <v>12668</v>
+      </c>
+      <c r="E834" s="5" t="s">
+        <v>12669</v>
+      </c>
+      <c r="F834" s="5" t="s">
+        <v>12666</v>
+      </c>
+      <c r="G834" s="5" t="s">
+        <v>12668</v>
+      </c>
+      <c r="H834" s="5" t="s">
+        <v>12668</v>
+      </c>
+      <c r="I834" s="5" t="s">
+        <v>12668</v>
+      </c>
+      <c r="J834" s="5" t="s">
+        <v>12668</v>
+      </c>
+      <c r="K834" s="5" t="s">
+        <v>12668</v>
+      </c>
+      <c r="L834" s="5" t="s">
+        <v>12668</v>
+      </c>
+      <c r="M834" s="5" t="s">
+        <v>12668</v>
+      </c>
+      <c r="N834" s="5" t="s">
+        <v>12668</v>
+      </c>
+      <c r="O834" s="5" t="s">
+        <v>12668</v>
+      </c>
+      <c r="P834" s="5" t="s">
+        <v>12668</v>
+      </c>
+      <c r="Q834" s="5" t="s">
+        <v>12668</v>
+      </c>
+      <c r="R834" s="5" t="s">
+        <v>12670</v>
+      </c>
+    </row>
+    <row r="835" customHeight="1" spans="1:18">
+      <c r="A835" s="5" t="s">
+        <v>12671</v>
+      </c>
+      <c r="B835" s="5" t="s">
+        <v>12672</v>
+      </c>
+      <c r="C835" s="5" t="s">
+        <v>12673</v>
+      </c>
+      <c r="D835" s="5" t="s">
+        <v>12674</v>
+      </c>
+      <c r="E835" s="5" t="s">
+        <v>12675</v>
+      </c>
+      <c r="F835" s="5" t="s">
+        <v>12676</v>
+      </c>
+      <c r="G835" s="5" t="s">
+        <v>12674</v>
+      </c>
+      <c r="H835" s="5" t="s">
+        <v>12674</v>
+      </c>
+      <c r="I835" s="5" t="s">
+        <v>12674</v>
+      </c>
+      <c r="J835" s="5" t="s">
+        <v>12674</v>
+      </c>
+      <c r="K835" s="5" t="s">
+        <v>12674</v>
+      </c>
+      <c r="L835" s="5" t="s">
+        <v>12674</v>
+      </c>
+      <c r="M835" s="5" t="s">
+        <v>12674</v>
+      </c>
+      <c r="N835" s="5" t="s">
+        <v>12674</v>
+      </c>
+      <c r="O835" s="5" t="s">
+        <v>12674</v>
+      </c>
+      <c r="P835" s="5" t="s">
+        <v>12674</v>
+      </c>
+      <c r="Q835" s="5" t="s">
+        <v>12674</v>
+      </c>
+      <c r="R835" s="5" t="s">
+        <v>12672</v>
+      </c>
+    </row>
+    <row r="836" customHeight="1" spans="1:18">
+      <c r="A836" s="5" t="s">
+        <v>12677</v>
+      </c>
+      <c r="B836" s="5" t="s">
+        <v>12678</v>
+      </c>
+      <c r="C836" s="5" t="s">
+        <v>12679</v>
+      </c>
+      <c r="D836" s="5" t="s">
+        <v>12680</v>
+      </c>
+      <c r="E836" s="5" t="s">
+        <v>12681</v>
+      </c>
+      <c r="F836" s="5" t="s">
+        <v>12682</v>
+      </c>
+      <c r="G836" s="5" t="s">
+        <v>12680</v>
+      </c>
+      <c r="H836" s="5" t="s">
+        <v>12680</v>
+      </c>
+      <c r="I836" s="5" t="s">
+        <v>12680</v>
+      </c>
+      <c r="J836" s="5" t="s">
+        <v>12680</v>
+      </c>
+      <c r="K836" s="5" t="s">
+        <v>12680</v>
+      </c>
+      <c r="L836" s="5" t="s">
+        <v>12680</v>
+      </c>
+      <c r="M836" s="5" t="s">
+        <v>12680</v>
+      </c>
+      <c r="N836" s="5" t="s">
+        <v>12680</v>
+      </c>
+      <c r="O836" s="5" t="s">
+        <v>12680</v>
+      </c>
+      <c r="P836" s="5" t="s">
+        <v>12680</v>
+      </c>
+      <c r="Q836" s="5" t="s">
+        <v>12680</v>
+      </c>
+      <c r="R836" s="5" t="s">
+        <v>12683</v>
+      </c>
+    </row>
+    <row r="837" customHeight="1" spans="1:18">
+      <c r="A837" s="5" t="s">
+        <v>12684</v>
+      </c>
+      <c r="B837" s="5" t="s">
+        <v>12685</v>
+      </c>
+      <c r="C837" s="5" t="s">
+        <v>12686</v>
+      </c>
+      <c r="D837" s="5" t="s">
+        <v>12687</v>
+      </c>
+      <c r="E837" s="5" t="s">
+        <v>12688</v>
+      </c>
+      <c r="F837" s="5" t="s">
+        <v>12689</v>
+      </c>
+      <c r="G837" s="5" t="s">
+        <v>12687</v>
+      </c>
+      <c r="H837" s="5" t="s">
+        <v>12687</v>
+      </c>
+      <c r="I837" s="5" t="s">
+        <v>12687</v>
+      </c>
+      <c r="J837" s="5" t="s">
+        <v>12687</v>
+      </c>
+      <c r="K837" s="5" t="s">
+        <v>12687</v>
+      </c>
+      <c r="L837" s="5" t="s">
+        <v>12687</v>
+      </c>
+      <c r="M837" s="5" t="s">
+        <v>12687</v>
+      </c>
+      <c r="N837" s="5" t="s">
+        <v>12687</v>
+      </c>
+      <c r="O837" s="5" t="s">
+        <v>12687</v>
+      </c>
+      <c r="P837" s="5" t="s">
+        <v>12687</v>
+      </c>
+      <c r="Q837" s="5" t="s">
+        <v>12687</v>
+      </c>
+      <c r="R837" s="5" t="s">
+        <v>12690</v>
+      </c>
+    </row>
+    <row r="838" customHeight="1" spans="1:18">
+      <c r="A838" s="5" t="s">
+        <v>12691</v>
+      </c>
+      <c r="B838" s="5" t="s">
+        <v>12692</v>
+      </c>
+      <c r="C838" s="5" t="s">
+        <v>12693</v>
+      </c>
+      <c r="D838" s="5" t="s">
+        <v>12694</v>
+      </c>
+      <c r="E838" s="5" t="s">
+        <v>12695</v>
+      </c>
+      <c r="F838" s="5" t="s">
+        <v>12696</v>
+      </c>
+      <c r="G838" s="5" t="s">
+        <v>12694</v>
+      </c>
+      <c r="H838" s="5" t="s">
+        <v>12694</v>
+      </c>
+      <c r="I838" s="5" t="s">
+        <v>12694</v>
+      </c>
+      <c r="J838" s="5" t="s">
+        <v>12694</v>
+      </c>
+      <c r="K838" s="5" t="s">
+        <v>12694</v>
+      </c>
+      <c r="L838" s="5" t="s">
+        <v>12694</v>
+      </c>
+      <c r="M838" s="5" t="s">
+        <v>12694</v>
+      </c>
+      <c r="N838" s="5" t="s">
+        <v>12694</v>
+      </c>
+      <c r="O838" s="5" t="s">
+        <v>12694</v>
+      </c>
+      <c r="P838" s="5" t="s">
+        <v>12694</v>
+      </c>
+      <c r="Q838" s="5" t="s">
+        <v>12694</v>
+      </c>
+      <c r="R838" s="5" t="s">
+        <v>12692</v>
+      </c>
+    </row>
+    <row r="839" customHeight="1" spans="1:18">
+      <c r="A839" s="5" t="s">
+        <v>12697</v>
+      </c>
+      <c r="B839" s="5" t="s">
+        <v>12698</v>
+      </c>
+      <c r="C839" s="5" t="s">
+        <v>12699</v>
+      </c>
+      <c r="D839" s="5" t="s">
+        <v>12700</v>
+      </c>
+      <c r="E839" s="5" t="s">
+        <v>12701</v>
+      </c>
+      <c r="F839" s="5" t="s">
+        <v>12702</v>
+      </c>
+      <c r="G839" s="5" t="s">
+        <v>12700</v>
+      </c>
+      <c r="H839" s="5" t="s">
+        <v>12700</v>
+      </c>
+      <c r="I839" s="5" t="s">
+        <v>12700</v>
+      </c>
+      <c r="J839" s="5" t="s">
+        <v>12700</v>
+      </c>
+      <c r="K839" s="5" t="s">
+        <v>12700</v>
+      </c>
+      <c r="L839" s="5" t="s">
+        <v>12700</v>
+      </c>
+      <c r="M839" s="5" t="s">
+        <v>12700</v>
+      </c>
+      <c r="N839" s="5" t="s">
+        <v>12700</v>
+      </c>
+      <c r="O839" s="5" t="s">
+        <v>12700</v>
+      </c>
+      <c r="P839" s="5" t="s">
+        <v>12700</v>
+      </c>
+      <c r="Q839" s="5" t="s">
+        <v>12700</v>
+      </c>
+      <c r="R839" s="5" t="s">
+        <v>12698</v>
+      </c>
+    </row>
+    <row r="840" customHeight="1" spans="1:18">
+      <c r="A840" s="5" t="s">
+        <v>12703</v>
+      </c>
+      <c r="B840" s="5" t="s">
+        <v>12704</v>
+      </c>
+      <c r="C840" s="5" t="s">
+        <v>12705</v>
+      </c>
+      <c r="D840" s="5" t="s">
+        <v>12706</v>
+      </c>
+      <c r="E840" s="5" t="s">
+        <v>12707</v>
+      </c>
+      <c r="F840" s="5" t="s">
+        <v>12708</v>
+      </c>
+      <c r="G840" s="5" t="s">
+        <v>12706</v>
+      </c>
+      <c r="H840" s="5" t="s">
+        <v>12706</v>
+      </c>
+      <c r="I840" s="5" t="s">
+        <v>12706</v>
+      </c>
+      <c r="J840" s="5" t="s">
+        <v>12706</v>
+      </c>
+      <c r="K840" s="5" t="s">
+        <v>12706</v>
+      </c>
+      <c r="L840" s="5" t="s">
+        <v>12706</v>
+      </c>
+      <c r="M840" s="5" t="s">
+        <v>12706</v>
+      </c>
+      <c r="N840" s="5" t="s">
+        <v>12706</v>
+      </c>
+      <c r="O840" s="5" t="s">
+        <v>12706</v>
+      </c>
+      <c r="P840" s="5" t="s">
+        <v>12706</v>
+      </c>
+      <c r="Q840" s="5" t="s">
+        <v>12706</v>
+      </c>
+      <c r="R840" s="5" t="s">
+        <v>12709</v>
+      </c>
+    </row>
+    <row r="841" customHeight="1" spans="1:18">
+      <c r="A841" s="5" t="s">
+        <v>12710</v>
+      </c>
+      <c r="B841" s="5" t="s">
+        <v>12711</v>
+      </c>
+      <c r="C841" s="5" t="s">
+        <v>12712</v>
+      </c>
+      <c r="D841" s="5" t="s">
+        <v>12713</v>
+      </c>
+      <c r="E841" s="5" t="s">
+        <v>12714</v>
+      </c>
+      <c r="F841" s="5" t="s">
+        <v>12715</v>
+      </c>
+      <c r="G841" s="5" t="s">
+        <v>12713</v>
+      </c>
+      <c r="H841" s="5" t="s">
+        <v>12713</v>
+      </c>
+      <c r="I841" s="5" t="s">
+        <v>12713</v>
+      </c>
+      <c r="J841" s="5" t="s">
+        <v>12713</v>
+      </c>
+      <c r="K841" s="5" t="s">
+        <v>12713</v>
+      </c>
+      <c r="L841" s="5" t="s">
+        <v>12713</v>
+      </c>
+      <c r="M841" s="5" t="s">
+        <v>12713</v>
+      </c>
+      <c r="N841" s="5" t="s">
+        <v>12713</v>
+      </c>
+      <c r="O841" s="5" t="s">
+        <v>12713</v>
+      </c>
+      <c r="P841" s="5" t="s">
+        <v>12713</v>
+      </c>
+      <c r="Q841" s="5" t="s">
+        <v>12713</v>
+      </c>
+      <c r="R841" s="5" t="s">
+        <v>12711</v>
+      </c>
+    </row>
+    <row r="842" customHeight="1" spans="1:18">
+      <c r="A842" s="5" t="s">
+        <v>12716</v>
+      </c>
+      <c r="B842" s="5" t="s">
+        <v>12717</v>
+      </c>
+      <c r="C842" s="5" t="s">
+        <v>12718</v>
+      </c>
+      <c r="D842" s="5" t="s">
+        <v>12719</v>
+      </c>
+      <c r="E842" s="5" t="s">
+        <v>12720</v>
+      </c>
+      <c r="F842" s="5" t="s">
+        <v>12721</v>
+      </c>
+      <c r="G842" s="5" t="s">
+        <v>12719</v>
+      </c>
+      <c r="H842" s="5" t="s">
+        <v>12719</v>
+      </c>
+      <c r="I842" s="5" t="s">
+        <v>12719</v>
+      </c>
+      <c r="J842" s="5" t="s">
+        <v>12719</v>
+      </c>
+      <c r="K842" s="5" t="s">
+        <v>12719</v>
+      </c>
+      <c r="L842" s="5" t="s">
+        <v>12719</v>
+      </c>
+      <c r="M842" s="5" t="s">
+        <v>12719</v>
+      </c>
+      <c r="N842" s="5" t="s">
+        <v>12719</v>
+      </c>
+      <c r="O842" s="5" t="s">
+        <v>12719</v>
+      </c>
+      <c r="P842" s="5" t="s">
+        <v>12719</v>
+      </c>
+      <c r="Q842" s="5" t="s">
+        <v>12719</v>
+      </c>
+      <c r="R842" s="5" t="s">
+        <v>12717</v>
+      </c>
+    </row>
+    <row r="843" customHeight="1" spans="1:18">
+      <c r="A843" s="5" t="s">
+        <v>12722</v>
+      </c>
+      <c r="B843" s="5" t="s">
+        <v>12723</v>
+      </c>
+      <c r="C843" s="5" t="s">
+        <v>12724</v>
+      </c>
+      <c r="D843" s="5" t="s">
+        <v>12725</v>
+      </c>
+      <c r="E843" s="5" t="s">
+        <v>12726</v>
+      </c>
+      <c r="F843" s="5" t="s">
+        <v>12727</v>
+      </c>
+      <c r="G843" s="5" t="s">
+        <v>12725</v>
+      </c>
+      <c r="H843" s="5" t="s">
+        <v>12725</v>
+      </c>
+      <c r="I843" s="5" t="s">
+        <v>12725</v>
+      </c>
+      <c r="J843" s="5" t="s">
+        <v>12725</v>
+      </c>
+      <c r="K843" s="5" t="s">
+        <v>12725</v>
+      </c>
+      <c r="L843" s="5" t="s">
+        <v>12725</v>
+      </c>
+      <c r="M843" s="5" t="s">
+        <v>12725</v>
+      </c>
+      <c r="N843" s="5" t="s">
+        <v>12725</v>
+      </c>
+      <c r="O843" s="5" t="s">
+        <v>12725</v>
+      </c>
+      <c r="P843" s="5" t="s">
+        <v>12725</v>
+      </c>
+      <c r="Q843" s="5" t="s">
+        <v>12725</v>
+      </c>
+      <c r="R843" s="5" t="s">
+        <v>12728</v>
+      </c>
+    </row>
+    <row r="844" customHeight="1" spans="1:18">
+      <c r="A844" s="5" t="s">
+        <v>12729</v>
+      </c>
+      <c r="B844" s="5" t="s">
+        <v>12730</v>
+      </c>
+      <c r="C844" s="5" t="s">
+        <v>12731</v>
+      </c>
+      <c r="D844" s="5" t="s">
+        <v>12731</v>
+      </c>
+      <c r="E844" s="5" t="s">
+        <v>12731</v>
+      </c>
+      <c r="F844" s="5" t="s">
+        <v>12732</v>
+      </c>
+      <c r="G844" s="5" t="s">
+        <v>12731</v>
+      </c>
+      <c r="H844" s="5" t="s">
+        <v>12731</v>
+      </c>
+      <c r="I844" s="5" t="s">
+        <v>12731</v>
+      </c>
+      <c r="J844" s="5" t="s">
+        <v>12731</v>
+      </c>
+      <c r="K844" s="5" t="s">
+        <v>12731</v>
+      </c>
+      <c r="L844" s="5" t="s">
+        <v>12731</v>
+      </c>
+      <c r="M844" s="5" t="s">
+        <v>12731</v>
+      </c>
+      <c r="N844" s="5" t="s">
+        <v>12731</v>
+      </c>
+      <c r="O844" s="5" t="s">
+        <v>12731</v>
+      </c>
+      <c r="P844" s="5" t="s">
+        <v>12731</v>
+      </c>
+      <c r="Q844" s="5" t="s">
+        <v>12731</v>
+      </c>
+      <c r="R844" s="5" t="s">
+        <v>12733</v>
+      </c>
+    </row>
+    <row r="845" customHeight="1" spans="1:18">
+      <c r="A845" s="5" t="s">
+        <v>12734</v>
+      </c>
+      <c r="B845" s="5" t="s">
+        <v>12735</v>
+      </c>
+      <c r="C845" s="5" t="s">
+        <v>12736</v>
+      </c>
+      <c r="D845" s="5" t="s">
+        <v>12736</v>
+      </c>
+      <c r="E845" s="5" t="s">
+        <v>12736</v>
+      </c>
+      <c r="F845" s="5" t="s">
+        <v>12737</v>
+      </c>
+      <c r="G845" s="5" t="s">
+        <v>12736</v>
+      </c>
+      <c r="H845" s="5" t="s">
+        <v>12736</v>
+      </c>
+      <c r="I845" s="5" t="s">
+        <v>12736</v>
+      </c>
+      <c r="J845" s="5" t="s">
+        <v>12736</v>
+      </c>
+      <c r="K845" s="5" t="s">
+        <v>12736</v>
+      </c>
+      <c r="L845" s="5" t="s">
+        <v>12736</v>
+      </c>
+      <c r="M845" s="5" t="s">
+        <v>12736</v>
+      </c>
+      <c r="N845" s="5" t="s">
+        <v>12736</v>
+      </c>
+      <c r="O845" s="5" t="s">
+        <v>12736</v>
+      </c>
+      <c r="P845" s="5" t="s">
+        <v>12736</v>
+      </c>
+      <c r="Q845" s="5" t="s">
+        <v>12736</v>
+      </c>
+      <c r="R845" s="5" t="s">
+        <v>12735</v>
+      </c>
+    </row>
+    <row r="846" customHeight="1" spans="1:18">
+      <c r="A846" s="5" t="s">
+        <v>12738</v>
+      </c>
+      <c r="B846" s="5" t="s">
+        <v>12739</v>
+      </c>
+      <c r="C846" s="5" t="s">
+        <v>12740</v>
+      </c>
+      <c r="D846" s="5" t="s">
+        <v>12740</v>
+      </c>
+      <c r="E846" s="5" t="s">
+        <v>12740</v>
+      </c>
+      <c r="F846" s="5" t="s">
+        <v>12741</v>
+      </c>
+      <c r="G846" s="5" t="s">
+        <v>12740</v>
+      </c>
+      <c r="H846" s="5" t="s">
+        <v>12740</v>
+      </c>
+      <c r="I846" s="5" t="s">
+        <v>12740</v>
+      </c>
+      <c r="J846" s="5" t="s">
+        <v>12740</v>
+      </c>
+      <c r="K846" s="5" t="s">
+        <v>12740</v>
+      </c>
+      <c r="L846" s="5" t="s">
+        <v>12740</v>
+      </c>
+      <c r="M846" s="5" t="s">
+        <v>12740</v>
+      </c>
+      <c r="N846" s="5" t="s">
+        <v>12740</v>
+      </c>
+      <c r="O846" s="5" t="s">
+        <v>12740</v>
+      </c>
+      <c r="P846" s="5" t="s">
+        <v>12740</v>
+      </c>
+      <c r="Q846" s="5" t="s">
+        <v>12740</v>
+      </c>
+      <c r="R846" s="5" t="s">
+        <v>12739</v>
+      </c>
+    </row>
+    <row r="847" customHeight="1" spans="1:18">
+      <c r="A847" s="5" t="s">
+        <v>12742</v>
+      </c>
+      <c r="B847" s="5" t="s">
+        <v>12743</v>
+      </c>
+      <c r="C847" s="5" t="s">
+        <v>12744</v>
+      </c>
+      <c r="D847" s="5" t="s">
+        <v>12744</v>
+      </c>
+      <c r="E847" s="5" t="s">
+        <v>12744</v>
+      </c>
+      <c r="F847" s="5" t="s">
+        <v>12745</v>
+      </c>
+      <c r="G847" s="5" t="s">
+        <v>12744</v>
+      </c>
+      <c r="H847" s="5" t="s">
+        <v>12744</v>
+      </c>
+      <c r="I847" s="5" t="s">
+        <v>12744</v>
+      </c>
+      <c r="J847" s="5" t="s">
+        <v>12744</v>
+      </c>
+      <c r="K847" s="5" t="s">
+        <v>12744</v>
+      </c>
+      <c r="L847" s="5" t="s">
+        <v>12744</v>
+      </c>
+      <c r="M847" s="5" t="s">
+        <v>12744</v>
+      </c>
+      <c r="N847" s="5" t="s">
+        <v>12744</v>
+      </c>
+      <c r="O847" s="5" t="s">
+        <v>12744</v>
+      </c>
+      <c r="P847" s="5" t="s">
+        <v>12744</v>
+      </c>
+      <c r="Q847" s="5" t="s">
+        <v>12744</v>
+      </c>
+      <c r="R847" s="5" t="s">
+        <v>12743</v>
+      </c>
+    </row>
+    <row r="848" customHeight="1" spans="1:18">
+      <c r="A848" s="5" t="s">
+        <v>12746</v>
+      </c>
+      <c r="B848" s="5" t="s">
+        <v>12747</v>
+      </c>
+      <c r="C848" s="5" t="s">
+        <v>12748</v>
+      </c>
+      <c r="D848" s="5" t="s">
+        <v>12748</v>
+      </c>
+      <c r="E848" s="5" t="s">
+        <v>12748</v>
+      </c>
+      <c r="F848" s="5" t="s">
+        <v>12749</v>
+      </c>
+      <c r="G848" s="5" t="s">
+        <v>12748</v>
+      </c>
+      <c r="H848" s="5" t="s">
+        <v>12748</v>
+      </c>
+      <c r="I848" s="5" t="s">
+        <v>12748</v>
+      </c>
+      <c r="J848" s="5" t="s">
+        <v>12748</v>
+      </c>
+      <c r="K848" s="5" t="s">
+        <v>12748</v>
+      </c>
+      <c r="L848" s="5" t="s">
+        <v>12748</v>
+      </c>
+      <c r="M848" s="5" t="s">
+        <v>12748</v>
+      </c>
+      <c r="N848" s="5" t="s">
+        <v>12748</v>
+      </c>
+      <c r="O848" s="5" t="s">
+        <v>12748</v>
+      </c>
+      <c r="P848" s="5" t="s">
+        <v>12748</v>
+      </c>
+      <c r="Q848" s="5" t="s">
+        <v>12748</v>
+      </c>
+      <c r="R848" s="5" t="s">
+        <v>12750</v>
+      </c>
+    </row>
+    <row r="849" customHeight="1" spans="1:18">
+      <c r="A849" s="5" t="s">
+        <v>12751</v>
+      </c>
+      <c r="B849" s="5" t="s">
+        <v>12752</v>
+      </c>
+      <c r="C849" s="5" t="s">
+        <v>12753</v>
+      </c>
+      <c r="D849" s="5" t="s">
+        <v>12753</v>
+      </c>
+      <c r="E849" s="5" t="s">
+        <v>12753</v>
+      </c>
+      <c r="F849" s="5" t="s">
+        <v>12754</v>
+      </c>
+      <c r="G849" s="5" t="s">
+        <v>12753</v>
+      </c>
+      <c r="H849" s="5" t="s">
+        <v>12753</v>
+      </c>
+      <c r="I849" s="5" t="s">
+        <v>12753</v>
+      </c>
+      <c r="J849" s="5" t="s">
+        <v>12753</v>
+      </c>
+      <c r="K849" s="5" t="s">
+        <v>12753</v>
+      </c>
+      <c r="L849" s="5" t="s">
+        <v>12753</v>
+      </c>
+      <c r="M849" s="5" t="s">
+        <v>12753</v>
+      </c>
+      <c r="N849" s="5" t="s">
+        <v>12753</v>
+      </c>
+      <c r="O849" s="5" t="s">
+        <v>12753</v>
+      </c>
+      <c r="P849" s="5" t="s">
+        <v>12753</v>
+      </c>
+      <c r="Q849" s="5" t="s">
+        <v>12753</v>
+      </c>
+      <c r="R849" s="5" t="s">
+        <v>12755</v>
+      </c>
+    </row>
+    <row r="850" customHeight="1" spans="1:18">
+      <c r="A850" s="5" t="s">
+        <v>12756</v>
+      </c>
+      <c r="B850" s="5" t="s">
+        <v>12757</v>
+      </c>
+      <c r="C850" s="5" t="s">
+        <v>12758</v>
+      </c>
+      <c r="D850" s="5" t="s">
+        <v>12758</v>
+      </c>
+      <c r="E850" s="5" t="s">
+        <v>12758</v>
+      </c>
+      <c r="F850" s="5" t="s">
+        <v>12759</v>
+      </c>
+      <c r="G850" s="5" t="s">
+        <v>12758</v>
+      </c>
+      <c r="H850" s="5" t="s">
+        <v>12758</v>
+      </c>
+      <c r="I850" s="5" t="s">
+        <v>12758</v>
+      </c>
+      <c r="J850" s="5" t="s">
+        <v>12758</v>
+      </c>
+      <c r="K850" s="5" t="s">
+        <v>12758</v>
+      </c>
+      <c r="L850" s="5" t="s">
+        <v>12758</v>
+      </c>
+      <c r="M850" s="5" t="s">
+        <v>12758</v>
+      </c>
+      <c r="N850" s="5" t="s">
+        <v>12758</v>
+      </c>
+      <c r="O850" s="5" t="s">
+        <v>12758</v>
+      </c>
+      <c r="P850" s="5" t="s">
+        <v>12758</v>
+      </c>
+      <c r="Q850" s="5" t="s">
+        <v>12758</v>
+      </c>
+      <c r="R850" s="5" t="s">
+        <v>12760</v>
+      </c>
+    </row>
+    <row r="851" customHeight="1" spans="1:18">
+      <c r="A851" s="5" t="s">
+        <v>12761</v>
+      </c>
+      <c r="B851" s="5" t="s">
+        <v>12762</v>
+      </c>
+      <c r="C851" s="5" t="s">
+        <v>12763</v>
+      </c>
+      <c r="D851" s="5" t="s">
+        <v>12763</v>
+      </c>
+      <c r="E851" s="5" t="s">
+        <v>12763</v>
+      </c>
+      <c r="F851" s="5" t="s">
+        <v>12764</v>
+      </c>
+      <c r="G851" s="5" t="s">
+        <v>12763</v>
+      </c>
+      <c r="H851" s="5" t="s">
+        <v>12763</v>
+      </c>
+      <c r="I851" s="5" t="s">
+        <v>12763</v>
+      </c>
+      <c r="J851" s="5" t="s">
+        <v>12763</v>
+      </c>
+      <c r="K851" s="5" t="s">
+        <v>12763</v>
+      </c>
+      <c r="L851" s="5" t="s">
+        <v>12763</v>
+      </c>
+      <c r="M851" s="5" t="s">
+        <v>12763</v>
+      </c>
+      <c r="N851" s="5" t="s">
+        <v>12763</v>
+      </c>
+      <c r="O851" s="5" t="s">
+        <v>12763</v>
+      </c>
+      <c r="P851" s="5" t="s">
+        <v>12763</v>
+      </c>
+      <c r="Q851" s="5" t="s">
+        <v>12763</v>
+      </c>
+      <c r="R851" s="5" t="s">
+        <v>12765</v>
+      </c>
+    </row>
+    <row r="852" customHeight="1" spans="1:18">
+      <c r="A852" s="5" t="s">
+        <v>12766</v>
+      </c>
+      <c r="B852" s="5" t="s">
+        <v>12767</v>
+      </c>
+      <c r="C852" s="5" t="s">
+        <v>12767</v>
+      </c>
+      <c r="D852" s="5" t="s">
+        <v>12767</v>
+      </c>
+      <c r="E852" s="5" t="s">
+        <v>12767</v>
+      </c>
+      <c r="F852" s="5" t="s">
+        <v>12767</v>
+      </c>
+      <c r="G852" s="5" t="s">
+        <v>12767</v>
+      </c>
+      <c r="H852" s="5" t="s">
+        <v>12767</v>
+      </c>
+      <c r="I852" s="5" t="s">
+        <v>12767</v>
+      </c>
+      <c r="J852" s="5" t="s">
+        <v>12767</v>
+      </c>
+      <c r="K852" s="5" t="s">
+        <v>12767</v>
+      </c>
+      <c r="L852" s="5" t="s">
+        <v>12767</v>
+      </c>
+      <c r="M852" s="5" t="s">
+        <v>12767</v>
+      </c>
+      <c r="N852" s="5" t="s">
+        <v>12767</v>
+      </c>
+      <c r="O852" s="5" t="s">
+        <v>12767</v>
+      </c>
+      <c r="P852" s="5" t="s">
+        <v>12767</v>
+      </c>
+      <c r="Q852" s="5" t="s">
+        <v>12767</v>
+      </c>
+      <c r="R852" s="5" t="s">
+        <v>12768</v>
+      </c>
+    </row>
+    <row r="853" customHeight="1" spans="1:18">
+      <c r="A853" s="5" t="s">
+        <v>12769</v>
+      </c>
+      <c r="B853" s="5" t="s">
+        <v>12770</v>
+      </c>
+      <c r="C853" s="5" t="s">
+        <v>12771</v>
+      </c>
+      <c r="D853" s="5" t="s">
+        <v>12771</v>
+      </c>
+      <c r="E853" s="5" t="s">
+        <v>12771</v>
+      </c>
+      <c r="F853" s="5" t="s">
+        <v>12772</v>
+      </c>
+      <c r="G853" s="5" t="s">
+        <v>12771</v>
+      </c>
+      <c r="H853" s="5" t="s">
+        <v>12771</v>
+      </c>
+      <c r="I853" s="5" t="s">
+        <v>12771</v>
+      </c>
+      <c r="J853" s="5" t="s">
+        <v>12771</v>
+      </c>
+      <c r="K853" s="5" t="s">
+        <v>12771</v>
+      </c>
+      <c r="L853" s="5" t="s">
+        <v>12771</v>
+      </c>
+      <c r="M853" s="5" t="s">
+        <v>12771</v>
+      </c>
+      <c r="N853" s="5" t="s">
+        <v>12771</v>
+      </c>
+      <c r="O853" s="5" t="s">
+        <v>12771</v>
+      </c>
+      <c r="P853" s="5" t="s">
+        <v>12771</v>
+      </c>
+      <c r="Q853" s="5" t="s">
+        <v>12771</v>
+      </c>
+      <c r="R853" s="5" t="s">
+        <v>12770</v>
+      </c>
+    </row>
+    <row r="854" customHeight="1" spans="1:18">
+      <c r="A854" s="5" t="s">
+        <v>12773</v>
+      </c>
+      <c r="B854" s="5" t="s">
+        <v>12774</v>
+      </c>
+      <c r="C854" s="5" t="s">
+        <v>12775</v>
+      </c>
+      <c r="D854" s="5" t="s">
+        <v>12775</v>
+      </c>
+      <c r="E854" s="5" t="s">
+        <v>12776</v>
+      </c>
+      <c r="F854" s="5" t="s">
+        <v>12776</v>
+      </c>
+      <c r="G854" s="5" t="s">
+        <v>12775</v>
+      </c>
+      <c r="H854" s="5" t="s">
+        <v>12775</v>
+      </c>
+      <c r="I854" s="5" t="s">
+        <v>12775</v>
+      </c>
+      <c r="J854" s="5" t="s">
+        <v>12775</v>
+      </c>
+      <c r="K854" s="5" t="s">
+        <v>12775</v>
+      </c>
+      <c r="L854" s="5" t="s">
+        <v>12775</v>
+      </c>
+      <c r="M854" s="5" t="s">
+        <v>12775</v>
+      </c>
+      <c r="N854" s="5" t="s">
+        <v>12775</v>
+      </c>
+      <c r="O854" s="5" t="s">
+        <v>12775</v>
+      </c>
+      <c r="P854" s="5" t="s">
+        <v>12775</v>
+      </c>
+      <c r="Q854" s="5" t="s">
+        <v>12775</v>
+      </c>
+      <c r="R854" s="5" t="s">
+        <v>12777</v>
+      </c>
+    </row>
+    <row r="855" customHeight="1" spans="1:18">
+      <c r="A855" s="5" t="s">
+        <v>12778</v>
+      </c>
+      <c r="B855" s="5" t="s">
+        <v>12779</v>
+      </c>
+      <c r="C855" s="5" t="s">
+        <v>12780</v>
+      </c>
+      <c r="D855" s="5" t="s">
+        <v>12780</v>
+      </c>
+      <c r="E855" s="5" t="s">
+        <v>12780</v>
+      </c>
+      <c r="F855" s="5" t="s">
+        <v>12781</v>
+      </c>
+      <c r="G855" s="5" t="s">
+        <v>12780</v>
+      </c>
+      <c r="H855" s="5" t="s">
+        <v>12780</v>
+      </c>
+      <c r="I855" s="5" t="s">
+        <v>12780</v>
+      </c>
+      <c r="J855" s="5" t="s">
+        <v>12780</v>
+      </c>
+      <c r="K855" s="5" t="s">
+        <v>12780</v>
+      </c>
+      <c r="L855" s="5" t="s">
+        <v>12780</v>
+      </c>
+      <c r="M855" s="5" t="s">
+        <v>12780</v>
+      </c>
+      <c r="N855" s="5" t="s">
+        <v>12780</v>
+      </c>
+      <c r="O855" s="5" t="s">
+        <v>12780</v>
+      </c>
+      <c r="P855" s="5" t="s">
+        <v>12780</v>
+      </c>
+      <c r="Q855" s="5" t="s">
+        <v>12780</v>
+      </c>
+      <c r="R855" s="5" t="s">
+        <v>12782</v>
+      </c>
+    </row>
+    <row r="856" customHeight="1" spans="1:18">
+      <c r="A856" s="5" t="s">
+        <v>12783</v>
+      </c>
+      <c r="B856" s="5" t="s">
+        <v>12784</v>
+      </c>
+      <c r="C856" s="5" t="s">
+        <v>12785</v>
+      </c>
+      <c r="D856" s="5" t="s">
+        <v>12785</v>
+      </c>
+      <c r="E856" s="5" t="s">
+        <v>12785</v>
+      </c>
+      <c r="F856" s="5" t="s">
+        <v>12786</v>
+      </c>
+      <c r="G856" s="5" t="s">
+        <v>12785</v>
+      </c>
+      <c r="H856" s="5" t="s">
+        <v>12785</v>
+      </c>
+      <c r="I856" s="5" t="s">
+        <v>12785</v>
+      </c>
+      <c r="J856" s="5" t="s">
+        <v>12785</v>
+      </c>
+      <c r="K856" s="5" t="s">
+        <v>12785</v>
+      </c>
+      <c r="L856" s="5" t="s">
+        <v>12785</v>
+      </c>
+      <c r="M856" s="5" t="s">
+        <v>12785</v>
+      </c>
+      <c r="N856" s="5" t="s">
+        <v>12785</v>
+      </c>
+      <c r="O856" s="5" t="s">
+        <v>12785</v>
+      </c>
+      <c r="P856" s="5" t="s">
+        <v>12785</v>
+      </c>
+      <c r="Q856" s="5" t="s">
+        <v>12785</v>
+      </c>
+      <c r="R856" s="5" t="s">
+        <v>12784</v>
+      </c>
+    </row>
+    <row r="857" customHeight="1" spans="1:18">
+      <c r="A857" s="5" t="s">
+        <v>12787</v>
+      </c>
+      <c r="B857" s="5" t="s">
+        <v>12788</v>
+      </c>
+      <c r="C857" s="5" t="s">
+        <v>12789</v>
+      </c>
+      <c r="D857" s="5" t="s">
+        <v>12789</v>
+      </c>
+      <c r="E857" s="5" t="s">
+        <v>12789</v>
+      </c>
+      <c r="F857" s="5" t="s">
+        <v>12790</v>
+      </c>
+      <c r="G857" s="5" t="s">
+        <v>12789</v>
+      </c>
+      <c r="H857" s="5" t="s">
+        <v>12789</v>
+      </c>
+      <c r="I857" s="5" t="s">
+        <v>12789</v>
+      </c>
+      <c r="J857" s="5" t="s">
+        <v>12789</v>
+      </c>
+      <c r="K857" s="5" t="s">
+        <v>12789</v>
+      </c>
+      <c r="L857" s="5" t="s">
+        <v>12789</v>
+      </c>
+      <c r="M857" s="5" t="s">
+        <v>12789</v>
+      </c>
+      <c r="N857" s="5" t="s">
+        <v>12789</v>
+      </c>
+      <c r="O857" s="5" t="s">
+        <v>12789</v>
+      </c>
+      <c r="P857" s="5" t="s">
+        <v>12789</v>
+      </c>
+      <c r="Q857" s="5" t="s">
+        <v>12789</v>
+      </c>
+      <c r="R857" s="5" t="s">
+        <v>12788</v>
+      </c>
+    </row>
+    <row r="858" customHeight="1" spans="1:18">
+      <c r="A858" s="5" t="s">
+        <v>12791</v>
+      </c>
+      <c r="B858" s="5" t="s">
+        <v>12792</v>
+      </c>
+      <c r="C858" s="5" t="s">
+        <v>12793</v>
+      </c>
+      <c r="D858" s="5" t="s">
+        <v>12794</v>
+      </c>
+      <c r="E858" s="5" t="s">
+        <v>12793</v>
+      </c>
+      <c r="F858" s="5" t="s">
+        <v>12795</v>
+      </c>
+      <c r="G858" s="5" t="s">
+        <v>12794</v>
+      </c>
+      <c r="H858" s="5" t="s">
+        <v>12794</v>
+      </c>
+      <c r="I858" s="5" t="s">
+        <v>12794</v>
+      </c>
+      <c r="J858" s="5" t="s">
+        <v>12794</v>
+      </c>
+      <c r="K858" s="5" t="s">
+        <v>12794</v>
+      </c>
+      <c r="L858" s="5" t="s">
+        <v>12794</v>
+      </c>
+      <c r="M858" s="5" t="s">
+        <v>12794</v>
+      </c>
+      <c r="N858" s="5" t="s">
+        <v>12794</v>
+      </c>
+      <c r="O858" s="5" t="s">
+        <v>12794</v>
+      </c>
+      <c r="P858" s="5" t="s">
+        <v>12794</v>
+      </c>
+      <c r="Q858" s="5" t="s">
+        <v>12794</v>
+      </c>
+      <c r="R858" s="5" t="s">
+        <v>12792</v>
+      </c>
+    </row>
+    <row r="859" customHeight="1" spans="1:18">
+      <c r="A859" s="5" t="s">
+        <v>12796</v>
+      </c>
+      <c r="B859" s="5" t="s">
+        <v>12797</v>
+      </c>
+      <c r="C859" s="5" t="s">
+        <v>12798</v>
+      </c>
+      <c r="D859" s="5" t="s">
+        <v>12798</v>
+      </c>
+      <c r="E859" s="5" t="s">
+        <v>12798</v>
+      </c>
+      <c r="F859" s="5" t="s">
+        <v>12799</v>
+      </c>
+      <c r="G859" s="5" t="s">
+        <v>12798</v>
+      </c>
+      <c r="H859" s="5" t="s">
+        <v>12798</v>
+      </c>
+      <c r="I859" s="5" t="s">
+        <v>12798</v>
+      </c>
+      <c r="J859" s="5" t="s">
+        <v>12798</v>
+      </c>
+      <c r="K859" s="5" t="s">
+        <v>12798</v>
+      </c>
+      <c r="L859" s="5" t="s">
+        <v>12798</v>
+      </c>
+      <c r="M859" s="5" t="s">
+        <v>12798</v>
+      </c>
+      <c r="N859" s="5" t="s">
+        <v>12798</v>
+      </c>
+      <c r="O859" s="5" t="s">
+        <v>12798</v>
+      </c>
+      <c r="P859" s="5" t="s">
+        <v>12798</v>
+      </c>
+      <c r="Q859" s="5" t="s">
+        <v>12798</v>
+      </c>
+      <c r="R859" s="5" t="s">
+        <v>12797</v>
+      </c>
+    </row>
+    <row r="860" customHeight="1" spans="1:18">
+      <c r="A860" s="5" t="s">
+        <v>12800</v>
+      </c>
+      <c r="B860" s="5" t="s">
+        <v>12801</v>
+      </c>
+      <c r="C860" s="5" t="s">
+        <v>12802</v>
+      </c>
+      <c r="D860" s="5" t="s">
+        <v>12802</v>
+      </c>
+      <c r="E860" s="5" t="s">
+        <v>12802</v>
+      </c>
+      <c r="F860" s="5" t="s">
+        <v>12803</v>
+      </c>
+      <c r="G860" s="5" t="s">
+        <v>12802</v>
+      </c>
+      <c r="H860" s="5" t="s">
+        <v>12802</v>
+      </c>
+      <c r="I860" s="5" t="s">
+        <v>12802</v>
+      </c>
+      <c r="J860" s="5" t="s">
+        <v>12802</v>
+      </c>
+      <c r="K860" s="5" t="s">
+        <v>12802</v>
+      </c>
+      <c r="L860" s="5" t="s">
+        <v>12802</v>
+      </c>
+      <c r="M860" s="5" t="s">
+        <v>12802</v>
+      </c>
+      <c r="N860" s="5" t="s">
+        <v>12802</v>
+      </c>
+      <c r="O860" s="5" t="s">
+        <v>12802</v>
+      </c>
+      <c r="P860" s="5" t="s">
+        <v>12802</v>
+      </c>
+      <c r="Q860" s="5" t="s">
+        <v>12802</v>
+      </c>
+      <c r="R860" s="5" t="s">
+        <v>12804</v>
+      </c>
+    </row>
+    <row r="861" customHeight="1" spans="1:18">
+      <c r="A861" s="5" t="s">
+        <v>12805</v>
+      </c>
+      <c r="B861" s="5" t="s">
+        <v>12806</v>
+      </c>
+      <c r="C861" s="5" t="s">
+        <v>12807</v>
+      </c>
+      <c r="D861" s="5" t="s">
+        <v>12807</v>
+      </c>
+      <c r="E861" s="5" t="s">
+        <v>12807</v>
+      </c>
+      <c r="F861" s="5" t="s">
+        <v>12808</v>
+      </c>
+      <c r="G861" s="5" t="s">
+        <v>12807</v>
+      </c>
+      <c r="H861" s="5" t="s">
+        <v>12807</v>
+      </c>
+      <c r="I861" s="5" t="s">
+        <v>12807</v>
+      </c>
+      <c r="J861" s="5" t="s">
+        <v>12807</v>
+      </c>
+      <c r="K861" s="5" t="s">
+        <v>12807</v>
+      </c>
+      <c r="L861" s="5" t="s">
+        <v>12807</v>
+      </c>
+      <c r="M861" s="5" t="s">
+        <v>12807</v>
+      </c>
+      <c r="N861" s="5" t="s">
+        <v>12807</v>
+      </c>
+      <c r="O861" s="5" t="s">
+        <v>12807</v>
+      </c>
+      <c r="P861" s="5" t="s">
+        <v>12807</v>
+      </c>
+      <c r="Q861" s="5" t="s">
+        <v>12807</v>
+      </c>
+      <c r="R861" s="5" t="s">
+        <v>12809</v>
+      </c>
+    </row>
+    <row r="862" customHeight="1" spans="1:18">
+      <c r="A862" s="5" t="s">
+        <v>12810</v>
+      </c>
+      <c r="B862" s="5" t="s">
+        <v>12811</v>
+      </c>
+      <c r="C862" s="5" t="s">
+        <v>12812</v>
+      </c>
+      <c r="D862" s="5" t="s">
+        <v>12812</v>
+      </c>
+      <c r="E862" s="5" t="s">
+        <v>12812</v>
+      </c>
+      <c r="F862" s="5" t="s">
+        <v>12813</v>
+      </c>
+      <c r="G862" s="5" t="s">
+        <v>12812</v>
+      </c>
+      <c r="H862" s="5" t="s">
+        <v>12812</v>
+      </c>
+      <c r="I862" s="5" t="s">
+        <v>12812</v>
+      </c>
+      <c r="J862" s="5" t="s">
+        <v>12812</v>
+      </c>
+      <c r="K862" s="5" t="s">
+        <v>12812</v>
+      </c>
+      <c r="L862" s="5" t="s">
+        <v>12812</v>
+      </c>
+      <c r="M862" s="5" t="s">
+        <v>12812</v>
+      </c>
+      <c r="N862" s="5" t="s">
+        <v>12812</v>
+      </c>
+      <c r="O862" s="5" t="s">
+        <v>12812</v>
+      </c>
+      <c r="P862" s="5" t="s">
+        <v>12812</v>
+      </c>
+      <c r="Q862" s="5" t="s">
+        <v>12812</v>
+      </c>
+      <c r="R862" s="5" t="s">
+        <v>12811</v>
+      </c>
+    </row>
+    <row r="863" customHeight="1" spans="1:18">
+      <c r="A863" s="5" t="s">
+        <v>12814</v>
+      </c>
+      <c r="B863" s="5" t="s">
+        <v>12815</v>
+      </c>
+      <c r="C863" s="5" t="s">
+        <v>12816</v>
+      </c>
+      <c r="D863" s="5" t="s">
+        <v>12816</v>
+      </c>
+      <c r="E863" s="5" t="s">
+        <v>12816</v>
+      </c>
+      <c r="F863" s="5" t="s">
+        <v>12817</v>
+      </c>
+      <c r="G863" s="5" t="s">
+        <v>12816</v>
+      </c>
+      <c r="H863" s="5" t="s">
+        <v>12816</v>
+      </c>
+      <c r="I863" s="5" t="s">
+        <v>12816</v>
+      </c>
+      <c r="J863" s="5" t="s">
+        <v>12816</v>
+      </c>
+      <c r="K863" s="5" t="s">
+        <v>12816</v>
+      </c>
+      <c r="L863" s="5" t="s">
+        <v>12816</v>
+      </c>
+      <c r="M863" s="5" t="s">
+        <v>12816</v>
+      </c>
+      <c r="N863" s="5" t="s">
+        <v>12816</v>
+      </c>
+      <c r="O863" s="5" t="s">
+        <v>12816</v>
+      </c>
+      <c r="P863" s="5" t="s">
+        <v>12816</v>
+      </c>
+      <c r="Q863" s="5" t="s">
+        <v>12816</v>
+      </c>
+      <c r="R863" s="5" t="s">
+        <v>12818</v>
+      </c>
+    </row>
+    <row r="864" customHeight="1" spans="1:18">
+      <c r="A864" s="5" t="s">
+        <v>12819</v>
+      </c>
+      <c r="B864" s="5" t="s">
+        <v>12820</v>
+      </c>
+      <c r="C864" s="5" t="s">
+        <v>12821</v>
+      </c>
+      <c r="D864" s="5" t="s">
+        <v>12821</v>
+      </c>
+      <c r="E864" s="5" t="s">
+        <v>12821</v>
+      </c>
+      <c r="F864" s="5" t="s">
+        <v>12822</v>
+      </c>
+      <c r="G864" s="5" t="s">
+        <v>12821</v>
+      </c>
+      <c r="H864" s="5" t="s">
+        <v>12821</v>
+      </c>
+      <c r="I864" s="5" t="s">
+        <v>12821</v>
+      </c>
+      <c r="J864" s="5" t="s">
+        <v>12821</v>
+      </c>
+      <c r="K864" s="5" t="s">
+        <v>12821</v>
+      </c>
+      <c r="L864" s="5" t="s">
+        <v>12821</v>
+      </c>
+      <c r="M864" s="5" t="s">
+        <v>12821</v>
+      </c>
+      <c r="N864" s="5" t="s">
+        <v>12821</v>
+      </c>
+      <c r="O864" s="5" t="s">
+        <v>12821</v>
+      </c>
+      <c r="P864" s="5" t="s">
+        <v>12821</v>
+      </c>
+      <c r="Q864" s="5" t="s">
+        <v>12821</v>
+      </c>
+      <c r="R864" s="5" t="s">
+        <v>12823</v>
+      </c>
+    </row>
+    <row r="865" customHeight="1" spans="1:18">
+      <c r="A865" s="5" t="s">
+        <v>12824</v>
+      </c>
+      <c r="B865" s="5" t="s">
+        <v>12825</v>
+      </c>
+      <c r="C865" s="5" t="s">
+        <v>12826</v>
+      </c>
+      <c r="D865" s="5" t="s">
+        <v>12826</v>
+      </c>
+      <c r="E865" s="5" t="s">
+        <v>12826</v>
+      </c>
+      <c r="F865" s="5" t="s">
+        <v>12827</v>
+      </c>
+      <c r="G865" s="5" t="s">
+        <v>12826</v>
+      </c>
+      <c r="H865" s="5" t="s">
+        <v>12826</v>
+      </c>
+      <c r="I865" s="5" t="s">
+        <v>12826</v>
+      </c>
+      <c r="J865" s="5" t="s">
+        <v>12826</v>
+      </c>
+      <c r="K865" s="5" t="s">
+        <v>12826</v>
+      </c>
+      <c r="L865" s="5" t="s">
+        <v>12826</v>
+      </c>
+      <c r="M865" s="5" t="s">
+        <v>12826</v>
+      </c>
+      <c r="N865" s="5" t="s">
+        <v>12826</v>
+      </c>
+      <c r="O865" s="5" t="s">
+        <v>12826</v>
+      </c>
+      <c r="P865" s="5" t="s">
+        <v>12826</v>
+      </c>
+      <c r="Q865" s="5" t="s">
+        <v>12826</v>
+      </c>
+      <c r="R865" s="5" t="s">
+        <v>12828</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A325" r:id="rId1" display="h5.contract.record.no"/>
